--- a/dataset_fixed.xlsx
+++ b/dataset_fixed.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3727" uniqueCount="1473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3727" uniqueCount="1474">
   <si>
     <t>Yemek_Id</t>
   </si>
@@ -4433,18 +4433,29 @@
   </si>
   <si>
     <t>Kahvalti_yan</t>
+  </si>
+  <si>
+    <t>Sakatat</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4560,48 +4571,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -13527,8 +13541,8 @@
       <c r="B184" s="5" t="s">
         <v>883</v>
       </c>
-      <c r="C184" s="5" t="s">
-        <v>564</v>
+      <c r="C184" t="s">
+        <v>1473</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>839</v>
@@ -19611,8 +19625,8 @@
       <c r="B311" s="8" t="s">
         <v>1337</v>
       </c>
-      <c r="C311" s="8" t="s">
-        <v>564</v>
+      <c r="C311" s="20" t="s">
+        <v>1473</v>
       </c>
       <c r="D311" s="8" t="s">
         <v>1148</v>
